--- a/templates/demo-criterion-gap.xlsx
+++ b/templates/demo-criterion-gap.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:T18"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -415,6 +415,10 @@
     <col min="14" max="14" width="12.83203125" customWidth="1"/>
     <col min="15" max="15" width="12.83203125" customWidth="1"/>
     <col min="16" max="16" width="12.83203125" customWidth="1"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1"/>
+    <col min="18" max="18" width="12.83203125" customWidth="1"/>
+    <col min="19" max="19" width="12.83203125" customWidth="1"/>
+    <col min="20" max="20" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -434,7 +438,7 @@
         <v/>
       </c>
       <c r="F1" t="str">
-        <v>Progress Report</v>
+        <v>Unit 2</v>
       </c>
       <c r="G1" t="str">
         <v/>
@@ -446,7 +450,7 @@
         <v/>
       </c>
       <c r="J1" t="str">
-        <v>End of Term</v>
+        <v>Progress Report</v>
       </c>
       <c r="K1" t="str">
         <v/>
@@ -458,12 +462,24 @@
         <v/>
       </c>
       <c r="N1" t="str">
-        <v/>
+        <v>End of Term</v>
       </c>
       <c r="O1" t="str">
         <v/>
       </c>
       <c r="P1" t="str">
+        <v/>
+      </c>
+      <c r="Q1" t="str">
+        <v/>
+      </c>
+      <c r="R1" t="str">
+        <v/>
+      </c>
+      <c r="S1" t="str">
+        <v/>
+      </c>
+      <c r="T1" t="str">
         <v/>
       </c>
     </row>
@@ -508,12 +524,24 @@
         <v>D</v>
       </c>
       <c r="N2" t="str">
+        <v>A</v>
+      </c>
+      <c r="O2" t="str">
+        <v>B</v>
+      </c>
+      <c r="P2" t="str">
+        <v>C</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>D</v>
+      </c>
+      <c r="R2" t="str">
         <v>Attendance %</v>
       </c>
-      <c r="O2" t="str">
+      <c r="S2" t="str">
         <v>Homework %</v>
       </c>
-      <c r="P2" t="str">
+      <c r="T2" t="str">
         <v>EAL</v>
       </c>
     </row>
@@ -524,14 +552,14 @@
       <c r="B3">
         <v>6</v>
       </c>
-      <c r="C3" t="str">
-        <v>—</v>
+      <c r="C3">
+        <v>3</v>
       </c>
       <c r="D3">
         <v>6</v>
       </c>
-      <c r="E3" t="str">
-        <v>—</v>
+      <c r="E3">
+        <v>5</v>
       </c>
       <c r="F3">
         <v>6</v>
@@ -540,13 +568,13 @@
         <v>3</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>5</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K3">
         <v>3</v>
@@ -558,12 +586,24 @@
         <v>5</v>
       </c>
       <c r="N3">
+        <v>7</v>
+      </c>
+      <c r="O3">
+        <v>3</v>
+      </c>
+      <c r="P3">
+        <v>6</v>
+      </c>
+      <c r="Q3">
+        <v>5</v>
+      </c>
+      <c r="R3">
         <v>96</v>
       </c>
-      <c r="O3">
+      <c r="S3">
         <v>100</v>
       </c>
-      <c r="P3" t="str">
+      <c r="T3" t="str">
         <v>No</v>
       </c>
     </row>
@@ -574,17 +614,17 @@
       <c r="B4">
         <v>7</v>
       </c>
-      <c r="C4" t="str">
-        <v>—</v>
+      <c r="C4">
+        <v>2</v>
       </c>
       <c r="D4">
         <v>6</v>
       </c>
-      <c r="E4" t="str">
-        <v>—</v>
+      <c r="E4">
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -608,12 +648,24 @@
         <v>6</v>
       </c>
       <c r="N4">
+        <v>7</v>
+      </c>
+      <c r="O4">
+        <v>2</v>
+      </c>
+      <c r="P4">
+        <v>6</v>
+      </c>
+      <c r="Q4">
+        <v>6</v>
+      </c>
+      <c r="R4">
         <v>98</v>
       </c>
-      <c r="O4">
+      <c r="S4">
         <v>92</v>
       </c>
-      <c r="P4" t="str">
+      <c r="T4" t="str">
         <v>No</v>
       </c>
     </row>
@@ -624,14 +676,14 @@
       <c r="B5">
         <v>5</v>
       </c>
-      <c r="C5" t="str">
-        <v>—</v>
+      <c r="C5">
+        <v>4</v>
       </c>
       <c r="D5">
         <v>5</v>
       </c>
-      <c r="E5" t="str">
-        <v>—</v>
+      <c r="E5">
+        <v>5</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -658,12 +710,24 @@
         <v>5</v>
       </c>
       <c r="N5">
+        <v>5</v>
+      </c>
+      <c r="O5">
+        <v>4</v>
+      </c>
+      <c r="P5">
+        <v>5</v>
+      </c>
+      <c r="Q5">
+        <v>5</v>
+      </c>
+      <c r="R5">
         <v>94</v>
       </c>
-      <c r="O5">
+      <c r="S5">
         <v>88</v>
       </c>
-      <c r="P5" t="str">
+      <c r="T5" t="str">
         <v>No</v>
       </c>
     </row>
@@ -674,29 +738,29 @@
       <c r="B6">
         <v>6</v>
       </c>
-      <c r="C6" t="str">
-        <v>—</v>
+      <c r="C6">
+        <v>3</v>
       </c>
       <c r="D6">
         <v>7</v>
       </c>
-      <c r="E6" t="str">
-        <v>—</v>
+      <c r="E6">
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6">
         <v>3</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>6</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>3</v>
@@ -708,12 +772,24 @@
         <v>6</v>
       </c>
       <c r="N6">
+        <v>7</v>
+      </c>
+      <c r="O6">
+        <v>3</v>
+      </c>
+      <c r="P6">
+        <v>7</v>
+      </c>
+      <c r="Q6">
+        <v>6</v>
+      </c>
+      <c r="R6">
         <v>91</v>
       </c>
-      <c r="O6">
+      <c r="S6">
         <v>96</v>
       </c>
-      <c r="P6" t="str">
+      <c r="T6" t="str">
         <v>Yes</v>
       </c>
     </row>
@@ -724,14 +800,14 @@
       <c r="B7">
         <v>6</v>
       </c>
-      <c r="C7" t="str">
-        <v>—</v>
+      <c r="C7">
+        <v>3</v>
       </c>
       <c r="D7">
         <v>6</v>
       </c>
-      <c r="E7" t="str">
-        <v>—</v>
+      <c r="E7">
+        <v>5</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -758,12 +834,24 @@
         <v>5</v>
       </c>
       <c r="N7">
+        <v>6</v>
+      </c>
+      <c r="O7">
+        <v>3</v>
+      </c>
+      <c r="P7">
+        <v>6</v>
+      </c>
+      <c r="Q7">
+        <v>5</v>
+      </c>
+      <c r="R7">
         <v>97</v>
       </c>
-      <c r="O7">
+      <c r="S7">
         <v>100</v>
       </c>
-      <c r="P7" t="str">
+      <c r="T7" t="str">
         <v>No</v>
       </c>
     </row>
@@ -774,17 +862,17 @@
       <c r="B8">
         <v>7</v>
       </c>
-      <c r="C8" t="str">
-        <v>—</v>
+      <c r="C8">
+        <v>4</v>
       </c>
       <c r="D8">
         <v>6</v>
       </c>
-      <c r="E8" t="str">
-        <v>—</v>
+      <c r="E8">
+        <v>6</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G8">
         <v>4</v>
@@ -808,12 +896,24 @@
         <v>6</v>
       </c>
       <c r="N8">
+        <v>7</v>
+      </c>
+      <c r="O8">
+        <v>4</v>
+      </c>
+      <c r="P8">
+        <v>6</v>
+      </c>
+      <c r="Q8">
+        <v>6</v>
+      </c>
+      <c r="R8">
         <v>99</v>
       </c>
-      <c r="O8">
+      <c r="S8">
         <v>94</v>
       </c>
-      <c r="P8" t="str">
+      <c r="T8" t="str">
         <v>No</v>
       </c>
     </row>
@@ -824,14 +924,14 @@
       <c r="B9">
         <v>5</v>
       </c>
-      <c r="C9" t="str">
-        <v>—</v>
+      <c r="C9">
+        <v>2</v>
       </c>
       <c r="D9">
         <v>5</v>
       </c>
-      <c r="E9" t="str">
-        <v>—</v>
+      <c r="E9">
+        <v>4</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -840,13 +940,13 @@
         <v>2</v>
       </c>
       <c r="H9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I9">
         <v>4</v>
       </c>
       <c r="J9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K9">
         <v>2</v>
@@ -858,12 +958,24 @@
         <v>4</v>
       </c>
       <c r="N9">
+        <v>6</v>
+      </c>
+      <c r="O9">
+        <v>2</v>
+      </c>
+      <c r="P9">
+        <v>5</v>
+      </c>
+      <c r="Q9">
+        <v>4</v>
+      </c>
+      <c r="R9">
         <v>95</v>
       </c>
-      <c r="O9">
+      <c r="S9">
         <v>90</v>
       </c>
-      <c r="P9" t="str">
+      <c r="T9" t="str">
         <v>No</v>
       </c>
     </row>
@@ -874,17 +986,17 @@
       <c r="B10">
         <v>6</v>
       </c>
-      <c r="C10" t="str">
-        <v>—</v>
+      <c r="C10">
+        <v>3</v>
       </c>
       <c r="D10">
         <v>6</v>
       </c>
-      <c r="E10" t="str">
-        <v>—</v>
+      <c r="E10">
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G10">
         <v>3</v>
@@ -908,12 +1020,24 @@
         <v>5</v>
       </c>
       <c r="N10">
+        <v>6</v>
+      </c>
+      <c r="O10">
+        <v>3</v>
+      </c>
+      <c r="P10">
+        <v>6</v>
+      </c>
+      <c r="Q10">
+        <v>5</v>
+      </c>
+      <c r="R10">
         <v>93</v>
       </c>
-      <c r="O10">
+      <c r="S10">
         <v>100</v>
       </c>
-      <c r="P10" t="str">
+      <c r="T10" t="str">
         <v>No</v>
       </c>
     </row>
@@ -924,14 +1048,14 @@
       <c r="B11">
         <v>8</v>
       </c>
-      <c r="C11" t="str">
-        <v>—</v>
+      <c r="C11">
+        <v>4</v>
       </c>
       <c r="D11">
         <v>7</v>
       </c>
-      <c r="E11" t="str">
-        <v>—</v>
+      <c r="E11">
+        <v>7</v>
       </c>
       <c r="F11">
         <v>8</v>
@@ -958,12 +1082,24 @@
         <v>7</v>
       </c>
       <c r="N11">
+        <v>8</v>
+      </c>
+      <c r="O11">
+        <v>4</v>
+      </c>
+      <c r="P11">
+        <v>7</v>
+      </c>
+      <c r="Q11">
+        <v>7</v>
+      </c>
+      <c r="R11">
         <v>98</v>
       </c>
-      <c r="O11">
+      <c r="S11">
         <v>86</v>
       </c>
-      <c r="P11" t="str">
+      <c r="T11" t="str">
         <v>No</v>
       </c>
     </row>
@@ -974,29 +1110,29 @@
       <c r="B12">
         <v>6</v>
       </c>
-      <c r="C12" t="str">
-        <v>—</v>
+      <c r="C12">
+        <v>3</v>
       </c>
       <c r="D12">
         <v>6</v>
       </c>
-      <c r="E12" t="str">
-        <v>—</v>
+      <c r="E12">
+        <v>5</v>
       </c>
       <c r="F12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G12">
         <v>3</v>
       </c>
       <c r="H12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I12">
         <v>5</v>
       </c>
       <c r="J12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K12">
         <v>3</v>
@@ -1008,12 +1144,24 @@
         <v>5</v>
       </c>
       <c r="N12">
+        <v>7</v>
+      </c>
+      <c r="O12">
+        <v>3</v>
+      </c>
+      <c r="P12">
+        <v>6</v>
+      </c>
+      <c r="Q12">
+        <v>5</v>
+      </c>
+      <c r="R12">
         <v>96</v>
       </c>
-      <c r="O12">
+      <c r="S12">
         <v>98</v>
       </c>
-      <c r="P12" t="str">
+      <c r="T12" t="str">
         <v>No</v>
       </c>
     </row>
@@ -1024,14 +1172,14 @@
       <c r="B13">
         <v>5</v>
       </c>
-      <c r="C13" t="str">
-        <v>—</v>
+      <c r="C13">
+        <v>3</v>
       </c>
       <c r="D13">
         <v>6</v>
       </c>
-      <c r="E13" t="str">
-        <v>—</v>
+      <c r="E13">
+        <v>5</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -1058,12 +1206,24 @@
         <v>5</v>
       </c>
       <c r="N13">
+        <v>5</v>
+      </c>
+      <c r="O13">
+        <v>3</v>
+      </c>
+      <c r="P13">
+        <v>6</v>
+      </c>
+      <c r="Q13">
+        <v>5</v>
+      </c>
+      <c r="R13">
         <v>92</v>
       </c>
-      <c r="O13">
+      <c r="S13">
         <v>92</v>
       </c>
-      <c r="P13" t="str">
+      <c r="T13" t="str">
         <v>Yes</v>
       </c>
     </row>
@@ -1074,17 +1234,17 @@
       <c r="B14">
         <v>6</v>
       </c>
-      <c r="C14" t="str">
-        <v>—</v>
+      <c r="C14">
+        <v>2</v>
       </c>
       <c r="D14">
         <v>5</v>
       </c>
-      <c r="E14" t="str">
-        <v>—</v>
+      <c r="E14">
+        <v>5</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1108,12 +1268,24 @@
         <v>5</v>
       </c>
       <c r="N14">
+        <v>6</v>
+      </c>
+      <c r="O14">
+        <v>2</v>
+      </c>
+      <c r="P14">
+        <v>5</v>
+      </c>
+      <c r="Q14">
+        <v>5</v>
+      </c>
+      <c r="R14">
         <v>97</v>
       </c>
-      <c r="O14">
+      <c r="S14">
         <v>100</v>
       </c>
-      <c r="P14" t="str">
+      <c r="T14" t="str">
         <v>No</v>
       </c>
     </row>
@@ -1124,14 +1296,14 @@
       <c r="B15">
         <v>7</v>
       </c>
-      <c r="C15" t="str">
-        <v>—</v>
+      <c r="C15">
+        <v>4</v>
       </c>
       <c r="D15">
         <v>6</v>
       </c>
-      <c r="E15" t="str">
-        <v>—</v>
+      <c r="E15">
+        <v>6</v>
       </c>
       <c r="F15">
         <v>7</v>
@@ -1140,30 +1312,42 @@
         <v>4</v>
       </c>
       <c r="H15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I15">
         <v>6</v>
       </c>
       <c r="J15">
+        <v>7</v>
+      </c>
+      <c r="K15">
+        <v>4</v>
+      </c>
+      <c r="L15">
+        <v>6</v>
+      </c>
+      <c r="M15">
+        <v>6</v>
+      </c>
+      <c r="N15">
         <v>8</v>
       </c>
-      <c r="K15">
-        <v>4</v>
-      </c>
-      <c r="L15">
-        <v>6</v>
-      </c>
-      <c r="M15">
-        <v>6</v>
-      </c>
-      <c r="N15">
+      <c r="O15">
+        <v>4</v>
+      </c>
+      <c r="P15">
+        <v>6</v>
+      </c>
+      <c r="Q15">
+        <v>6</v>
+      </c>
+      <c r="R15">
         <v>95</v>
       </c>
-      <c r="O15">
+      <c r="S15">
         <v>88</v>
       </c>
-      <c r="P15" t="str">
+      <c r="T15" t="str">
         <v>No</v>
       </c>
     </row>
@@ -1174,17 +1358,17 @@
       <c r="B16">
         <v>6</v>
       </c>
-      <c r="C16" t="str">
-        <v>—</v>
+      <c r="C16">
+        <v>3</v>
       </c>
       <c r="D16">
         <v>7</v>
       </c>
-      <c r="E16" t="str">
-        <v>—</v>
+      <c r="E16">
+        <v>6</v>
       </c>
       <c r="F16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G16">
         <v>3</v>
@@ -1208,12 +1392,24 @@
         <v>6</v>
       </c>
       <c r="N16">
+        <v>6</v>
+      </c>
+      <c r="O16">
+        <v>3</v>
+      </c>
+      <c r="P16">
+        <v>7</v>
+      </c>
+      <c r="Q16">
+        <v>6</v>
+      </c>
+      <c r="R16">
         <v>94</v>
       </c>
-      <c r="O16">
+      <c r="S16">
         <v>94</v>
       </c>
-      <c r="P16" t="str">
+      <c r="T16" t="str">
         <v>No</v>
       </c>
     </row>
@@ -1224,14 +1420,14 @@
       <c r="B17">
         <v>6</v>
       </c>
-      <c r="C17" t="str">
-        <v>—</v>
+      <c r="C17">
+        <v>3</v>
       </c>
       <c r="D17">
         <v>6</v>
       </c>
-      <c r="E17" t="str">
-        <v>—</v>
+      <c r="E17">
+        <v>5</v>
       </c>
       <c r="F17">
         <v>6</v>
@@ -1258,12 +1454,24 @@
         <v>5</v>
       </c>
       <c r="N17">
+        <v>6</v>
+      </c>
+      <c r="O17">
+        <v>3</v>
+      </c>
+      <c r="P17">
+        <v>6</v>
+      </c>
+      <c r="Q17">
+        <v>5</v>
+      </c>
+      <c r="R17">
         <v>99</v>
       </c>
-      <c r="O17">
+      <c r="S17">
         <v>96</v>
       </c>
-      <c r="P17" t="str">
+      <c r="T17" t="str">
         <v>No</v>
       </c>
     </row>
@@ -1274,29 +1482,29 @@
       <c r="B18">
         <v>5</v>
       </c>
-      <c r="C18" t="str">
-        <v>—</v>
+      <c r="C18">
+        <v>4</v>
       </c>
       <c r="D18">
         <v>6</v>
       </c>
-      <c r="E18" t="str">
-        <v>—</v>
+      <c r="E18">
+        <v>5</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18">
         <v>4</v>
       </c>
       <c r="H18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I18">
         <v>5</v>
       </c>
       <c r="J18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K18">
         <v>4</v>
@@ -1308,18 +1516,30 @@
         <v>5</v>
       </c>
       <c r="N18">
+        <v>6</v>
+      </c>
+      <c r="O18">
+        <v>4</v>
+      </c>
+      <c r="P18">
+        <v>6</v>
+      </c>
+      <c r="Q18">
+        <v>5</v>
+      </c>
+      <c r="R18">
         <v>96</v>
       </c>
-      <c r="O18">
+      <c r="S18">
         <v>90</v>
       </c>
-      <c r="P18" t="str">
+      <c r="T18" t="str">
         <v>No</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T18"/>
   </ignoredErrors>
 </worksheet>
 </file>